--- a/MSME/Test upload format/MSME_Continuity - 1.xlsx
+++ b/MSME/Test upload format/MSME_Continuity - 1.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +56,7 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357192</t>
+    <t>CGMSMGEN2210202600357238</t>
   </si>
   <si>
     <t>Aloan01</t>
@@ -65,139 +65,139 @@
     <t>Standard</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357193</t>
+    <t>CGMSMGEN2210202600357239</t>
   </si>
   <si>
     <t>Aloan02</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357194</t>
+    <t>CGMSMGEN2210202600357240</t>
   </si>
   <si>
     <t>Aloan03</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357195</t>
+    <t>CGMSMGEN2210202600357241</t>
   </si>
   <si>
     <t>Aloan04</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357196</t>
+    <t>CGMSMGEN2210202600357242</t>
   </si>
   <si>
     <t>Aloan05</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357197</t>
+    <t>CGMSMGEN2210202600357243</t>
   </si>
   <si>
     <t>Aloan06</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357198</t>
+    <t>CGMSMGEN2210202600357244</t>
   </si>
   <si>
     <t>Aloan07</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357199</t>
+    <t>CGMSMGEN2210202600357245</t>
   </si>
   <si>
     <t>Aloan08</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357200</t>
+    <t>CGMSMGEN2210202600357246</t>
   </si>
   <si>
     <t>Aloan09</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357201</t>
+    <t>CGMSMGEN2210202600357247</t>
   </si>
   <si>
     <t>Aloan10</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357202</t>
+    <t>CGMSMGEN2210202600357248</t>
   </si>
   <si>
     <t>Aloan11</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357203</t>
+    <t>CGMSMGEN2210202600357249</t>
   </si>
   <si>
     <t>Aloan12</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357204</t>
+    <t>CGMSMGEN2210202600357250</t>
   </si>
   <si>
     <t>Aloan13</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357205</t>
+    <t>CGMSMGEN2210202600357251</t>
   </si>
   <si>
     <t>Aloan14</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357206</t>
+    <t>CGMSMGEN2210202600357252</t>
   </si>
   <si>
     <t>Aloan15</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357207</t>
+    <t>CGMSMGEN2210202600357253</t>
   </si>
   <si>
     <t>Aloan16</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357208</t>
+    <t>CGMSMGEN2210202600357254</t>
   </si>
   <si>
     <t>Aloan17</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357209</t>
+    <t>CGMSMGEN2210202600357255</t>
   </si>
   <si>
     <t>Aloan18</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357210</t>
+    <t>CGMSMGEN2210202600357256</t>
   </si>
   <si>
     <t>Aloan19</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357211</t>
+    <t>CGMSMGEN2210202600357257</t>
   </si>
   <si>
     <t>Aloan20</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357212</t>
+    <t>CGMSMGEN2210202600357258</t>
   </si>
   <si>
     <t>Aloan21</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357213</t>
+    <t>CGMSMGEN2210202600357259</t>
   </si>
   <si>
     <t>Aloan22</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357214</t>
+    <t>CGMSMGEN2210202600357260</t>
   </si>
   <si>
     <t>Aloan23</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357215</t>
+    <t>CGMSMGEN2210202600357261</t>
   </si>
   <si>
     <t>Aloan24</t>
@@ -399,18 +399,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -740,7 +734,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -764,16 +758,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -782,90 +776,90 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -882,7 +876,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1198,16 +1191,16 @@
       <c r="B2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>200000000</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="9"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A3" s="6" t="s">
@@ -1216,16 +1209,16 @@
       <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>500000000</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="10"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A4" s="6" t="s">
@@ -1234,72 +1227,72 @@
       <c r="B4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>300000000</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>300000000</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" ht="15" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>300000000</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="9"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" ht="15" spans="1:8">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>460000000</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10"/>
+      <c r="F7" s="9"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
@@ -1310,16 +1303,16 @@
       <c r="B8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>100000000</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="10"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
@@ -1330,16 +1323,16 @@
       <c r="B9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>100000000</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="10"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
@@ -1350,250 +1343,250 @@
       <c r="B10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>100000000</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>0</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="10"/>
+      <c r="F10" s="9"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
     <row r="11" ht="15" spans="1:8">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>100000000</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="10"/>
+      <c r="F11" s="9"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
     <row r="12" ht="15" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>100000000</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" ht="15" spans="1:8">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>10000000</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="10"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" ht="15" spans="1:8">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>200000000</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" ht="15" spans="1:8">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>500000000</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="10"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
     <row r="16" ht="15" spans="1:8">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>300000000</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="10"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" ht="15" spans="1:8">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>300000000</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" ht="15" spans="1:8">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>300000000</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>0</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
     <row r="19" ht="15" spans="1:8">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>460000000</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" ht="15" spans="1:8">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>100000000</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
     <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>100000000</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="10"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
     <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>100000000</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -1601,16 +1594,16 @@
       </c>
     </row>
     <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>100000000</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -1618,16 +1611,16 @@
       </c>
     </row>
     <row r="24" ht="15" spans="1:8">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>100000000</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -1635,16 +1628,16 @@
       </c>
     </row>
     <row r="25" ht="15" spans="1:8">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>10000000</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -1652,7 +1645,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H21" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H25" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
